--- a/Hoadon/HDVao/8/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/8/HDDienTuMayTinhTien.xlsx
@@ -313,56 +313,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MVX</t>
+          <t>C25MBL</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>430979</t>
+          <t>716593</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>18/08/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0316158113-006</t>
+          <t>0104831030-091</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KHÍ HÓA LỎNG VIỆT NAM - VT GAS - CHI NHÁNH VŨNG TÀU</t>
+          <t>Chi nhánh Công ty TNHH NN một thành viên TM &amp; XNK Viettel – Trung tâm Bán lẻ</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Đường số 3, Khu Công Nghiệp Đông Xuyên, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Tòa nhà Hương Giang, số 1 ngõ 11 Duy Tân, phường Cầu Giấy, Thành phố Hà Nội, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502551856</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>CÔNG TY TNHH ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="13" t="n">
-        <v>462963.0</v>
+        <v>1.9435185E7</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>37037.0</v>
+        <v>1554815.0</v>
       </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>500000.0</v>
+        <v>2.099E7</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -370,6 +370,801 @@
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>C25MHA</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>27115810</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>30/08/2025</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>0110269067</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DI CHUYỂN XANH VÀ THÔNG MINH GSM</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Tòa Văn phòng Symphony, Đường Chu Huy Mân, Khu đô thị Vinhomes Riverside, Phường Phúc Lợi, Thành phố Hà Nội, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K8" s="6"/>
+      <c r="L8" s="13" t="n">
+        <v>34424.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>2576.0</v>
+      </c>
+      <c r="N8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O8" s="13" t="n">
+        <v>37000.0</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>C25MHM</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>458659</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>02/08/2025</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>0110269067-014</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH BÀ RỊA - VŨNG TÀU – CÔNG TY CỔ PHẦN DI CHUYỂN XANH VÀ THÔNG MINH GSM</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>1169/7 Đường 30/4, Phường Phước Thắng, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K9" s="6"/>
+      <c r="L9" s="13" t="n">
+        <v>50000.0</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>4000.0</v>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="13" t="n">
+        <v>54000.0</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>C25MHM</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>694614</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>30/08/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>0110269067-014</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH BÀ RỊA - VŨNG TÀU – CÔNG TY CỔ PHẦN DI CHUYỂN XANH VÀ THÔNG MINH GSM</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>1169/7 Đường 30/4, Phường Phước Thắng, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K10" s="6"/>
+      <c r="L10" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>2963.0</v>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>40000.0</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>C25MMD</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>15179</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>15/08/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>3500354108</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>DOANH NGHIỆP TƯ NHÂN XĂNG DẦU LONG PHƯỚC</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Số 3 Trần Phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH Đại Lý Tàu Biển Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="K11" s="6"/>
+      <c r="L11" s="13" t="n">
+        <v>626500.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>50120.0</v>
+      </c>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13" t="n">
+        <v>676620.0</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C25MMD</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>15180</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>15/08/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3500354108</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>DOANH NGHIỆP TƯ NHÂN XĂNG DẦU LONG PHƯỚC</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Số 3 Trần Phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH Đại Lý Tàu Biển Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="K12" s="6"/>
+      <c r="L12" s="13" t="n">
+        <v>70000.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>7000.0</v>
+      </c>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>77000.0</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C25MVT</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>04/08/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3502326113</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI VÀ DỊCH VỤ XÂY DỰNG HÒA PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>408 Thống Nhất (Mới), Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K13" s="6"/>
+      <c r="L13" s="13" t="n">
+        <v>268519.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>21481.0</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>290000.0</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C25MHV</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3502493509</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HÙNG VƯƠNG PHÚ MỸ</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Số 56 Đường Hùng Vương, Phường Phú Mỹ, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K14" s="6"/>
+      <c r="L14" s="13" t="n">
+        <v>3441000.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>289720.0</v>
+      </c>
+      <c r="N14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>3730720.0</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn đã bị thay thế</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C25MHV</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>956</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>06/08/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3502493509</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HÙNG VƯƠNG PHÚ MỸ</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Số 56 Đường Hùng Vương, Phường Phú Mỹ, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K15" s="6"/>
+      <c r="L15" s="13" t="n">
+        <v>3666982.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>307799.0</v>
+      </c>
+      <c r="N15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="13" t="n">
+        <v>3974781.0</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn đã bị thay thế</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C25MHV</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>07/08/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3502493509</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HÙNG VƯƠNG PHÚ MỸ</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Số 56 Đường Hùng Vương, Phường Phú Mỹ, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K16" s="6"/>
+      <c r="L16" s="13" t="n">
+        <v>3680353.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>294428.0</v>
+      </c>
+      <c r="N16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="13" t="n">
+        <v>3974781.0</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn thay thế</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C25MHV</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>07/08/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3502493509</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HÙNG VƯƠNG PHÚ MỸ</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Số 56 Đường Hùng Vương, Phường Phú Mỹ, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K17" s="6"/>
+      <c r="L17" s="13" t="n">
+        <v>3454371.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>276350.0</v>
+      </c>
+      <c r="N17" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O17" s="13" t="n">
+        <v>3730721.0</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn thay thế</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>C25MDV</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>4620</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>8937693982-001</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH DAVID PIZZA</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>92 Đường Hạ Long, Phường Vũng Tàu,Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K18" s="6"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="13" t="n">
+        <v>744000.0</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>
